--- a/data/trans_dic/P3A$otraNOcobra-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,71</t>
+          <t>3,7; 6,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,15</t>
+          <t>3,68; 6,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,96</t>
+          <t>3,96; 5,81</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,44</t>
+          <t>1,23; 3,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,65</t>
+          <t>3,6; 5,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,11</t>
+          <t>2,23; 4,13</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,6</t>
+          <t>1,49; 3,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,29</t>
+          <t>1,73; 5,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,01</t>
+          <t>1,97; 4,01</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,34</t>
+          <t>2,02; 5,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,91</t>
+          <t>2,31; 3,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,16</t>
+          <t>2,43; 4,06</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,77</t>
+          <t>2,29; 3,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,47</t>
+          <t>3,16; 4,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,98</t>
+          <t>2,92; 3,95</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23935; 42577</t>
+          <t>23464; 41767</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27506; 44601</t>
+          <t>26694; 44214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55648; 81021</t>
+          <t>53805; 79050</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14093; 41055</t>
+          <t>14727; 41613</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35743; 54127</t>
+          <t>34542; 54215</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46585; 88490</t>
+          <t>47881; 88892</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10265; 25346</t>
+          <t>10473; 26668</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17501; 49344</t>
+          <t>16121; 48787</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32865; 65667</t>
+          <t>32282; 65660</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18475; 49447</t>
+          <t>18740; 49501</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25270; 42763</t>
+          <t>25251; 43285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48819; 84083</t>
+          <t>49100; 81914</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80790; 130554</t>
+          <t>79067; 129235</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>118675; 165885</t>
+          <t>117353; 167125</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>219839; 285265</t>
+          <t>209298; 283026</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraNOcobra-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,58</t>
+          <t>3,41; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,1</t>
+          <t>3,99; 6,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 5,81</t>
+          <t>4,15; 5,91</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,49</t>
+          <t>2,09; 3,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,66</t>
+          <t>3,53; 5,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,13</t>
+          <t>3,02; 4,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,78</t>
+          <t>1,49; 3,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,23</t>
+          <t>3,66; 6,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,01</t>
+          <t>2,78; 4,38</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,34</t>
+          <t>1,74; 3,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,96</t>
+          <t>2,45; 4,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,06</t>
+          <t>2,31; 3,55</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,74</t>
+          <t>2,52; 3,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,5</t>
+          <t>3,75; 4,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,95</t>
+          <t>3,33; 4,03</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35315</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67024</t>
+          <t>69750</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23464; 41767</t>
+          <t>23511; 43645</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26694; 44214</t>
+          <t>29310; 45845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53805; 79050</t>
+          <t>59149; 84167</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28431</t>
+          <t>30240</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72271</t>
+          <t>77667</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14727; 41613</t>
+          <t>21944; 40809</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34542; 54215</t>
+          <t>37846; 56808</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47881; 88892</t>
+          <t>64079; 90495</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>38424</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>57140</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10473; 26668</t>
+          <t>11985; 29201</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16121; 48787</t>
+          <t>29762; 49522</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32282; 65660</t>
+          <t>44831; 70761</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61660</t>
+          <t>60830</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18740; 49501</t>
+          <t>17255; 36986</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25251; 43285</t>
+          <t>27375; 45227</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49100; 81914</t>
+          <t>48673; 74803</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>146841</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251965</t>
+          <t>265387</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>79067; 129235</t>
+          <t>88936; 127027</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>117353; 167125</t>
+          <t>140113; 177963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>209298; 283026</t>
+          <t>241658; 293041</t>
         </is>
       </c>
     </row>
